--- a/Mumbai-April-2025.xlsx
+++ b/Mumbai-April-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="107">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Mumbai</t>
   </si>
   <si>
@@ -292,25 +295,25 @@
     <t>MH02GH2432</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>ETIOS</t>
   </si>
   <si>
-    <t>HYRIDER</t>
-  </si>
-  <si>
-    <t>Fortuner</t>
-  </si>
-  <si>
-    <t>CITRON</t>
+    <t>HYRYDER</t>
+  </si>
+  <si>
+    <t>FORTUNER</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>DZIRE</t>
   </si>
   <si>
-    <t>BYD</t>
+    <t>BYD E6</t>
   </si>
   <si>
     <t>CAMRY</t>
@@ -322,25 +325,25 @@
     <t>Hycross</t>
   </si>
   <si>
-    <t>Merc E</t>
-  </si>
-  <si>
-    <t>5 Series</t>
+    <t>MERCEDES E</t>
+  </si>
+  <si>
+    <t>5 SERIES</t>
   </si>
   <si>
     <t>URBANIA</t>
   </si>
   <si>
     <t>XUV 400</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -393,11 +396,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,10 +696,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z65"/>
+  <dimension ref="A1:AA65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,27 +778,30 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>113</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2">
+        <v>93</v>
+      </c>
+      <c r="G2" s="2">
         <v>43579</v>
       </c>
       <c r="H2">
@@ -855,26 +862,26 @@
         <v>58.21</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3">
+        <v>93</v>
+      </c>
+      <c r="G3" s="2">
         <v>43579</v>
       </c>
       <c r="H3">
@@ -935,26 +942,26 @@
         <v>52.35</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4">
+        <v>93</v>
+      </c>
+      <c r="G4" s="2">
         <v>44470</v>
       </c>
       <c r="H4">
@@ -1015,27 +1022,27 @@
         <v>54.68</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" t="s">
-        <v>106</v>
+        <v>93</v>
+      </c>
+      <c r="G5" s="2">
+        <v>43328</v>
       </c>
       <c r="H5">
         <v>104680</v>
@@ -1095,26 +1102,26 @@
         <v>47.67</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6">
+        <v>93</v>
+      </c>
+      <c r="G6" s="2">
         <v>43554</v>
       </c>
       <c r="H6">
@@ -1175,27 +1182,27 @@
         <v>72.59</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" t="s">
-        <v>106</v>
+        <v>93</v>
+      </c>
+      <c r="G7" s="2">
+        <v>43581</v>
       </c>
       <c r="H7">
         <v>250678</v>
@@ -1255,26 +1262,26 @@
         <v>52.04</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>119</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8">
+        <v>93</v>
+      </c>
+      <c r="G8" s="2">
         <v>43501</v>
       </c>
       <c r="H8">
@@ -1335,26 +1342,26 @@
         <v>60.6</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9">
+        <v>93</v>
+      </c>
+      <c r="G9" s="2">
         <v>43708</v>
       </c>
       <c r="H9">
@@ -1415,26 +1422,26 @@
         <v>56.99</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>121</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10">
+        <v>93</v>
+      </c>
+      <c r="G10" s="2">
         <v>44663</v>
       </c>
       <c r="H10">
@@ -1495,26 +1502,26 @@
         <v>36.86</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>122</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11">
+        <v>93</v>
+      </c>
+      <c r="G11" s="2">
         <v>44663</v>
       </c>
       <c r="H11">
@@ -1575,26 +1582,26 @@
         <v>55.54</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>123</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12">
+        <v>93</v>
+      </c>
+      <c r="G12" s="2">
         <v>44663</v>
       </c>
       <c r="H12">
@@ -1655,26 +1662,26 @@
         <v>32.67</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13">
+        <v>93</v>
+      </c>
+      <c r="G13" s="2">
         <v>44686</v>
       </c>
       <c r="H13">
@@ -1735,26 +1742,26 @@
         <v>23.96</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14">
+        <v>93</v>
+      </c>
+      <c r="G14" s="2">
         <v>44686</v>
       </c>
       <c r="H14">
@@ -1815,26 +1822,26 @@
         <v>-19.59</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>126</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15">
+        <v>93</v>
+      </c>
+      <c r="G15" s="2">
         <v>44760</v>
       </c>
       <c r="H15">
@@ -1895,26 +1902,26 @@
         <v>21.41</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16">
+        <v>93</v>
+      </c>
+      <c r="G16" s="2">
         <v>44791</v>
       </c>
       <c r="H16">
@@ -1980,21 +1987,21 @@
         <v>128</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17">
+        <v>93</v>
+      </c>
+      <c r="G17" s="2">
         <v>44855</v>
       </c>
       <c r="H17">
@@ -2060,21 +2067,21 @@
         <v>129</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18">
+        <v>93</v>
+      </c>
+      <c r="G18" s="2">
         <v>44236</v>
       </c>
       <c r="H18">
@@ -2140,21 +2147,21 @@
         <v>130</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19">
+        <v>93</v>
+      </c>
+      <c r="G19" s="2">
         <v>43899</v>
       </c>
       <c r="H19">
@@ -2220,21 +2227,21 @@
         <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2">
         <v>43738</v>
       </c>
       <c r="H20">
@@ -2300,21 +2307,21 @@
         <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21">
+        <v>93</v>
+      </c>
+      <c r="G21" s="2">
         <v>44280</v>
       </c>
       <c r="H21">
@@ -2380,21 +2387,21 @@
         <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22">
+        <v>93</v>
+      </c>
+      <c r="G22" s="2">
         <v>43738</v>
       </c>
       <c r="H22">
@@ -2460,21 +2467,21 @@
         <v>134</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23">
+        <v>93</v>
+      </c>
+      <c r="G23" s="2">
         <v>44236</v>
       </c>
       <c r="H23">
@@ -2540,21 +2547,21 @@
         <v>135</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24">
+        <v>93</v>
+      </c>
+      <c r="G24" s="2">
         <v>43643</v>
       </c>
       <c r="H24">
@@ -2620,21 +2627,21 @@
         <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25">
+        <v>93</v>
+      </c>
+      <c r="G25" s="2">
         <v>44236</v>
       </c>
       <c r="H25">
@@ -2700,21 +2707,21 @@
         <v>137</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26">
+        <v>93</v>
+      </c>
+      <c r="G26" s="2">
         <v>44237</v>
       </c>
       <c r="H26">
@@ -2780,21 +2787,21 @@
         <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
-      </c>
-      <c r="G27">
+        <v>93</v>
+      </c>
+      <c r="G27" s="2">
         <v>43481</v>
       </c>
       <c r="H27">
@@ -2860,21 +2867,21 @@
         <v>139</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>92</v>
-      </c>
-      <c r="G28">
+        <v>93</v>
+      </c>
+      <c r="G28" s="2">
         <v>44470</v>
       </c>
       <c r="H28">
@@ -2940,21 +2947,21 @@
         <v>140</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>92</v>
-      </c>
-      <c r="G29">
+        <v>93</v>
+      </c>
+      <c r="G29" s="2">
         <v>44490</v>
       </c>
       <c r="H29">
@@ -3020,21 +3027,21 @@
         <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
-      </c>
-      <c r="G30">
+        <v>93</v>
+      </c>
+      <c r="G30" s="2">
         <v>43808</v>
       </c>
       <c r="H30">
@@ -3100,21 +3107,21 @@
         <v>142</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>92</v>
-      </c>
-      <c r="G31">
+        <v>93</v>
+      </c>
+      <c r="G31" s="2">
         <v>43808</v>
       </c>
       <c r="H31">
@@ -3180,21 +3187,21 @@
         <v>143</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32">
+        <v>93</v>
+      </c>
+      <c r="G32" s="2">
         <v>45596</v>
       </c>
       <c r="H32">
@@ -3260,21 +3267,21 @@
         <v>144</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>92</v>
-      </c>
-      <c r="G33">
+        <v>93</v>
+      </c>
+      <c r="G33" s="2">
         <v>45715</v>
       </c>
       <c r="H33">
@@ -3340,21 +3347,21 @@
         <v>145</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>92</v>
-      </c>
-      <c r="G34">
+        <v>93</v>
+      </c>
+      <c r="G34" s="2">
         <v>45715</v>
       </c>
       <c r="H34">
@@ -3420,21 +3427,21 @@
         <v>146</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>92</v>
-      </c>
-      <c r="G35">
+        <v>93</v>
+      </c>
+      <c r="G35" s="2">
         <v>45715</v>
       </c>
       <c r="H35">
@@ -3500,22 +3507,22 @@
         <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>93</v>
-      </c>
-      <c r="G36" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="G36" s="2">
+        <v>43554</v>
       </c>
       <c r="H36">
         <v>195538</v>
@@ -3580,22 +3587,22 @@
         <v>148</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2025</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>93</v>
-      </c>
-      <c r="G37" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="G37" s="2">
+        <v>43738</v>
       </c>
       <c r="H37">
         <v>100760</v>
@@ -3660,21 +3667,21 @@
         <v>149</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>2025</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>93</v>
-      </c>
-      <c r="G38">
+        <v>94</v>
+      </c>
+      <c r="G38" s="2">
         <v>43738</v>
       </c>
       <c r="H38">
@@ -3740,22 +3747,22 @@
         <v>150</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>2025</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>93</v>
-      </c>
-      <c r="G39" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="G39" s="2">
+        <v>43739</v>
       </c>
       <c r="H39">
         <v>92495</v>
@@ -3820,22 +3827,22 @@
         <v>151</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>2025</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F40" t="s">
-        <v>93</v>
-      </c>
-      <c r="G40" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="G40" s="2">
+        <v>44469</v>
       </c>
       <c r="H40">
         <v>174815</v>
@@ -3900,21 +3907,21 @@
         <v>152</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>2025</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
-        <v>94</v>
-      </c>
-      <c r="G41">
+        <v>95</v>
+      </c>
+      <c r="G41" s="2">
         <v>45573</v>
       </c>
       <c r="H41">
@@ -3980,22 +3987,22 @@
         <v>153</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>2025</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>95</v>
-      </c>
-      <c r="G42" t="s">
-        <v>106</v>
+        <v>96</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45030</v>
       </c>
       <c r="H42">
         <v>47932</v>
@@ -4060,21 +4067,21 @@
         <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43">
         <v>2025</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>96</v>
-      </c>
-      <c r="G43">
+        <v>97</v>
+      </c>
+      <c r="G43" s="2">
         <v>45510</v>
       </c>
       <c r="H43">
@@ -4140,21 +4147,21 @@
         <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44">
         <v>2025</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G44">
+        <v>97</v>
+      </c>
+      <c r="G44" s="2">
         <v>45510</v>
       </c>
       <c r="H44">
@@ -4220,21 +4227,21 @@
         <v>156</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>2025</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G45">
+        <v>98</v>
+      </c>
+      <c r="G45" s="2">
         <v>44991</v>
       </c>
       <c r="H45">
@@ -4300,21 +4307,21 @@
         <v>157</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46">
         <v>2025</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
-        <v>97</v>
-      </c>
-      <c r="G46">
+        <v>98</v>
+      </c>
+      <c r="G46" s="2">
         <v>44991</v>
       </c>
       <c r="H46">
@@ -4380,21 +4387,21 @@
         <v>158</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47">
         <v>2025</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>97</v>
-      </c>
-      <c r="G47">
+        <v>98</v>
+      </c>
+      <c r="G47" s="2">
         <v>45625</v>
       </c>
       <c r="H47">
@@ -4460,21 +4467,21 @@
         <v>159</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48">
         <v>2025</v>
       </c>
       <c r="E48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G48">
+        <v>98</v>
+      </c>
+      <c r="G48" s="2">
         <v>44868</v>
       </c>
       <c r="H48">
@@ -4540,21 +4547,21 @@
         <v>160</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D49">
         <v>2025</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F49" t="s">
-        <v>97</v>
-      </c>
-      <c r="G49">
+        <v>98</v>
+      </c>
+      <c r="G49" s="2">
         <v>45664</v>
       </c>
       <c r="H49">
@@ -4620,21 +4627,21 @@
         <v>161</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D50">
         <v>2025</v>
       </c>
       <c r="E50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F50" t="s">
-        <v>98</v>
-      </c>
-      <c r="G50">
+        <v>99</v>
+      </c>
+      <c r="G50" s="2">
         <v>44972</v>
       </c>
       <c r="H50">
@@ -4700,21 +4707,21 @@
         <v>162</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D51">
         <v>2025</v>
       </c>
       <c r="E51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F51" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51">
+        <v>100</v>
+      </c>
+      <c r="G51" s="2">
         <v>44719</v>
       </c>
       <c r="H51">
@@ -4780,21 +4787,21 @@
         <v>163</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D52">
         <v>2025</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
-        <v>99</v>
-      </c>
-      <c r="G52">
+        <v>100</v>
+      </c>
+      <c r="G52" s="2">
         <v>44686</v>
       </c>
       <c r="H52">
@@ -4860,21 +4867,21 @@
         <v>164</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D53">
         <v>2025</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F53" t="s">
-        <v>100</v>
-      </c>
-      <c r="G53">
+        <v>101</v>
+      </c>
+      <c r="G53" s="2">
         <v>45520</v>
       </c>
       <c r="H53">
@@ -4940,21 +4947,21 @@
         <v>165</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D54">
         <v>2025</v>
       </c>
       <c r="E54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G54">
+        <v>101</v>
+      </c>
+      <c r="G54" s="2">
         <v>45520</v>
       </c>
       <c r="H54">
@@ -5020,21 +5027,21 @@
         <v>166</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D55">
         <v>2025</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F55" t="s">
-        <v>100</v>
-      </c>
-      <c r="G55">
+        <v>101</v>
+      </c>
+      <c r="G55" s="2">
         <v>45520</v>
       </c>
       <c r="H55">
@@ -5100,21 +5107,21 @@
         <v>167</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D56">
         <v>2025</v>
       </c>
       <c r="E56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s">
-        <v>101</v>
-      </c>
-      <c r="G56">
+        <v>102</v>
+      </c>
+      <c r="G56" s="2">
         <v>44987</v>
       </c>
       <c r="H56">
@@ -5180,21 +5187,21 @@
         <v>168</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D57">
         <v>2025</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F57" t="s">
-        <v>101</v>
-      </c>
-      <c r="G57">
+        <v>102</v>
+      </c>
+      <c r="G57" s="2">
         <v>45279</v>
       </c>
       <c r="H57">
@@ -5260,21 +5267,21 @@
         <v>169</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58">
         <v>2025</v>
       </c>
       <c r="E58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s">
-        <v>102</v>
-      </c>
-      <c r="G58">
+        <v>103</v>
+      </c>
+      <c r="G58" s="2">
         <v>45769</v>
       </c>
       <c r="H58">
@@ -5340,21 +5347,21 @@
         <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59">
         <v>2025</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F59" t="s">
-        <v>103</v>
-      </c>
-      <c r="G59">
+        <v>104</v>
+      </c>
+      <c r="G59" s="2">
         <v>43908</v>
       </c>
       <c r="H59">
@@ -5420,21 +5427,21 @@
         <v>171</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D60">
         <v>2025</v>
       </c>
       <c r="E60" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F60" t="s">
-        <v>104</v>
-      </c>
-      <c r="G60">
+        <v>105</v>
+      </c>
+      <c r="G60" s="2">
         <v>45649</v>
       </c>
       <c r="H60">
@@ -5500,21 +5507,21 @@
         <v>172</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D61">
         <v>2025</v>
       </c>
       <c r="E61" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F61" t="s">
-        <v>104</v>
-      </c>
-      <c r="G61">
+        <v>105</v>
+      </c>
+      <c r="G61" s="2">
         <v>45649</v>
       </c>
       <c r="H61">
@@ -5580,21 +5587,21 @@
         <v>173</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D62">
         <v>2025</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F62" t="s">
-        <v>104</v>
-      </c>
-      <c r="G62">
+        <v>105</v>
+      </c>
+      <c r="G62" s="2">
         <v>45649</v>
       </c>
       <c r="H62">
@@ -5660,21 +5667,21 @@
         <v>174</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D63">
         <v>2025</v>
       </c>
       <c r="E63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G63">
+        <v>105</v>
+      </c>
+      <c r="G63" s="2">
         <v>45679</v>
       </c>
       <c r="H63">
@@ -5740,21 +5747,21 @@
         <v>175</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D64">
         <v>2025</v>
       </c>
       <c r="E64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F64" t="s">
-        <v>105</v>
-      </c>
-      <c r="G64">
+        <v>106</v>
+      </c>
+      <c r="G64" s="2">
         <v>45625</v>
       </c>
       <c r="H64">
@@ -5820,21 +5827,21 @@
         <v>176</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D65">
         <v>2025</v>
       </c>
       <c r="E65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F65" t="s">
-        <v>105</v>
-      </c>
-      <c r="G65">
+        <v>106</v>
+      </c>
+      <c r="G65" s="2">
         <v>45625</v>
       </c>
       <c r="H65">
